--- a/download/Attendance_Tracker_Monthly_July_2026.xlsx
+++ b/download/Attendance_Tracker_Monthly_July_2026.xlsx
@@ -9593,13 +9593,13 @@
         </is>
       </c>
       <c r="AI7" s="11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AJ7" s="11" t="n">
         <v>6</v>
       </c>
       <c r="AK7" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL7" s="6" t="inlineStr">
         <is>
